--- a/sports_forms/002_tournament_spectator_facilities_survey--sports_forms.xlsx
+++ b/sports_forms/002_tournament_spectator_facilities_survey--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1003,_'name':_'food_and_drinks',_'label':_'food_and_drinks'}</t>
+          <t>food_and_drinks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1003, 'name': 'food_and_drinks', 'label': 'Food and drinks'}</t>
+          <t>Food and drinks</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1004,_'name':_'merchandise',_'label':_'merchandise'}</t>
+          <t>merchandise</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1004, 'name': 'merchandise', 'label': 'Merchandise'}</t>
+          <t>Merchandise</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1005,_'name':_'parking',_'label':_'parking'}</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1005, 'name': 'parking', 'label': 'Parking'}</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1006,_'name':_'security',_'label':_'security'}</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1006, 'name': 'security', 'label': 'Security'}</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
